--- a/out/S01_campus_cafeteria_experience/agent5/agent5_qc_report.xlsx
+++ b/out/S01_campus_cafeteria_experience/agent5/agent5_qc_report.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
